--- a/naver-place-crawler/results_health/연제구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/연제구_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="Q2" t="n">
         <v>1520</v>
       </c>
       <c r="R2" t="n">
-        <v>2940</v>
+        <v>2943</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>템플짐 연산점 헬스&amp;PT</t>
+          <t>리드헬스&amp;PT&amp;기구필라테스 연산점24시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alswl1933@naver.com</t>
+          <t>lead8132@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1368-1876</t>
+          <t>0507-1356-8132</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 163 스타메디컬빌딩 8층</t>
+          <t>부산광역시 연제구 고분로13번길 25 한창타워 3층 내 리드헬스(301호~303호)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/alswl1933</t>
+          <t>https://www.instagram.com/lead_health.pt.pilates/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>503</v>
+        <v>702</v>
       </c>
       <c r="Q3" t="n">
-        <v>378</v>
+        <v>1582</v>
       </c>
       <c r="R3" t="n">
-        <v>881</v>
+        <v>2284</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2059297467</t>
+          <t>1311686124</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2059297467</t>
+          <t>https://m.place.naver.com/place/1311686124</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리드헬스&amp;PT&amp;기구필라테스 연산점24시</t>
+          <t>템플짐 연산점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lead8132@naver.com</t>
+          <t>alswl1933@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1356-8132</t>
+          <t>0507-1368-1876</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로13번길 25 한창타워 3층 내 리드헬스(301호~303호)</t>
+          <t>부산광역시 연제구 연수로 163 스타메디컬빌딩 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lead_health.pt.pilates/</t>
+          <t>https://blog.naver.com/alswl1933</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>702</v>
+        <v>504</v>
       </c>
       <c r="Q4" t="n">
-        <v>1576</v>
+        <v>378</v>
       </c>
       <c r="R4" t="n">
-        <v>2278</v>
+        <v>882</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1311686124</t>
+          <t>2059297467</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311686124</t>
+          <t>https://m.place.naver.com/place/2059297467</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,44 +846,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>글래드휘트니스 시청점</t>
+          <t>스탠다드짐 연산토곡점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gladfitness_cityhall@naver.com</t>
+          <t>standardgym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>051-868-0045</t>
+          <t>0507-1325-2235</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 34 시청역SK뷰 아파트 상가 3층</t>
+          <t>부산광역시 연제구 고분로236번길 13 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/585952?theme=place&amp;entry=pll&amp;area=pll</t>
+          <t>https://www.instagram.com/standardgym___4/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1095</v>
+        <v>188</v>
       </c>
       <c r="Q5" t="n">
-        <v>806</v>
+        <v>133</v>
       </c>
       <c r="R5" t="n">
-        <v>1901</v>
+        <v>321</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1703558578</t>
+          <t>2056534999</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703558578</t>
+          <t>https://m.place.naver.com/place/2056534999</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q6" t="n">
         <v>421</v>
       </c>
       <c r="R6" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q9" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="R9" t="n">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
